--- a/plots/map-data.xlsx
+++ b/plots/map-data.xlsx
@@ -82,16 +82,16 @@
     <t xml:space="preserve">ALB</t>
   </si>
   <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Submitted,
 data from 1990-2022</t>
   </si>
   <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Andorra</t>
   </si>
   <si>
@@ -102,61 +102,61 @@
   </si>
   <si>
     <t xml:space="preserve">ARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Samoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French Southern and Antarctic Lands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antigua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbuda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azerbaijan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZE</t>
   </si>
   <si>
     <t xml:space="preserve">Submitted,
 partial data up to 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Samoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French Southern and Antarctic Lands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antigua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbuda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azerbaijan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZE</t>
   </si>
   <si>
     <t xml:space="preserve">Burundi</t>
@@ -1938,18 +1938,18 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1971,37 +1971,37 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -2009,21 +2009,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16"/>
       <c r="C16" t="s">
@@ -2051,24 +2051,24 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -2079,7 +2079,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -2090,7 +2090,7 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -2112,7 +2112,7 @@
         <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -2134,7 +2134,7 @@
         <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -2145,7 +2145,7 @@
         <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
@@ -2189,7 +2189,7 @@
         <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -2200,7 +2200,7 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -2233,7 +2233,7 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -2255,7 +2255,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
@@ -2266,7 +2266,7 @@
         <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
@@ -2299,7 +2299,7 @@
         <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
@@ -2310,7 +2310,7 @@
         <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -2321,7 +2321,7 @@
         <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -2332,7 +2332,7 @@
         <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
@@ -2398,7 +2398,7 @@
         <v>106</v>
       </c>
       <c r="C48" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
@@ -2431,7 +2431,7 @@
         <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
@@ -2442,7 +2442,7 @@
         <v>114</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -2475,7 +2475,7 @@
         <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -2486,7 +2486,7 @@
         <v>122</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -2497,7 +2497,7 @@
         <v>124</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -2530,7 +2530,7 @@
         <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -2552,7 +2552,7 @@
         <v>134</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
@@ -2574,7 +2574,7 @@
         <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -2605,7 +2605,7 @@
         <v>143</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
@@ -2616,7 +2616,7 @@
         <v>145</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
@@ -2715,7 +2715,7 @@
         <v>163</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -2746,7 +2746,7 @@
         <v>168</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -2757,7 +2757,7 @@
         <v>170</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -2768,7 +2768,7 @@
         <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -2790,7 +2790,7 @@
         <v>176</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
@@ -2823,7 +2823,7 @@
         <v>182</v>
       </c>
       <c r="C87" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88">
@@ -2845,7 +2845,7 @@
         <v>186</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
@@ -2867,7 +2867,7 @@
         <v>190</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -2878,7 +2878,7 @@
         <v>192</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
@@ -2900,7 +2900,7 @@
         <v>196</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -2931,7 +2931,7 @@
         <v>201</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -2953,7 +2953,7 @@
         <v>205</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -2964,7 +2964,7 @@
         <v>207</v>
       </c>
       <c r="C100" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
@@ -3028,7 +3028,7 @@
         <v>218</v>
       </c>
       <c r="C106" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
@@ -3050,7 +3050,7 @@
         <v>222</v>
       </c>
       <c r="C108" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109">
@@ -3061,7 +3061,7 @@
         <v>224</v>
       </c>
       <c r="C109" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110">
@@ -3072,7 +3072,7 @@
         <v>226</v>
       </c>
       <c r="C110" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111">
@@ -3083,7 +3083,7 @@
         <v>228</v>
       </c>
       <c r="C111" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
@@ -3127,7 +3127,7 @@
         <v>236</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116">
@@ -3138,7 +3138,7 @@
         <v>238</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117">
@@ -3158,7 +3158,7 @@
         <v>241</v>
       </c>
       <c r="C118" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119">
@@ -3169,7 +3169,7 @@
         <v>243</v>
       </c>
       <c r="C119" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120">
@@ -3235,7 +3235,7 @@
         <v>254</v>
       </c>
       <c r="C125" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
@@ -3266,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="C128" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129">
@@ -3277,7 +3277,7 @@
         <v>261</v>
       </c>
       <c r="C129" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130">
@@ -3321,7 +3321,7 @@
         <v>269</v>
       </c>
       <c r="C133" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134">
@@ -3354,7 +3354,7 @@
         <v>275</v>
       </c>
       <c r="C136" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="137">
@@ -3365,7 +3365,7 @@
         <v>277</v>
       </c>
       <c r="C137" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138">
@@ -3376,7 +3376,7 @@
         <v>279</v>
       </c>
       <c r="C138" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="139">
@@ -3396,7 +3396,7 @@
         <v>282</v>
       </c>
       <c r="C140" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141">
@@ -3407,7 +3407,7 @@
         <v>284</v>
       </c>
       <c r="C141" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="142">
@@ -3418,7 +3418,7 @@
         <v>286</v>
       </c>
       <c r="C142" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143">
@@ -3440,7 +3440,7 @@
         <v>290</v>
       </c>
       <c r="C144" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145">
@@ -3451,7 +3451,7 @@
         <v>292</v>
       </c>
       <c r="C145" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="146">
@@ -3495,7 +3495,7 @@
         <v>300</v>
       </c>
       <c r="C149" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150">
@@ -3528,7 +3528,7 @@
         <v>306</v>
       </c>
       <c r="C152" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153">
@@ -3583,7 +3583,7 @@
         <v>316</v>
       </c>
       <c r="C157" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="158">
@@ -3605,7 +3605,7 @@
         <v>320</v>
       </c>
       <c r="C159" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160">
@@ -3616,7 +3616,7 @@
         <v>322</v>
       </c>
       <c r="C160" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="161">
@@ -3660,7 +3660,7 @@
         <v>330</v>
       </c>
       <c r="C164" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165">
@@ -3720,7 +3720,7 @@
         <v>339</v>
       </c>
       <c r="C170" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="171">
@@ -3731,7 +3731,7 @@
         <v>341</v>
       </c>
       <c r="C171" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172">
@@ -3742,7 +3742,7 @@
         <v>343</v>
       </c>
       <c r="C172" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="173">
@@ -3764,7 +3764,7 @@
         <v>347</v>
       </c>
       <c r="C174" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="175">
@@ -3775,7 +3775,7 @@
         <v>349</v>
       </c>
       <c r="C175" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="176">
@@ -3797,7 +3797,7 @@
         <v>353</v>
       </c>
       <c r="C177" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178">
@@ -3819,7 +3819,7 @@
         <v>357</v>
       </c>
       <c r="C179" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="180">
@@ -3863,7 +3863,7 @@
         <v>365</v>
       </c>
       <c r="C183" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="184">
@@ -3914,7 +3914,7 @@
         <v>373</v>
       </c>
       <c r="C188" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189">
@@ -3969,7 +3969,7 @@
         <v>383</v>
       </c>
       <c r="C193" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="194">
@@ -3980,7 +3980,7 @@
         <v>385</v>
       </c>
       <c r="C194" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195">
@@ -3991,7 +3991,7 @@
         <v>387</v>
       </c>
       <c r="C195" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="196">
@@ -4013,7 +4013,7 @@
         <v>391</v>
       </c>
       <c r="C197" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="198">
@@ -4057,7 +4057,7 @@
         <v>399</v>
       </c>
       <c r="C201" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="202">
@@ -4110,7 +4110,7 @@
         <v>407</v>
       </c>
       <c r="C206" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="207">
@@ -4165,7 +4165,7 @@
         <v>417</v>
       </c>
       <c r="C211" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="212">
@@ -4198,7 +4198,7 @@
         <v>423</v>
       </c>
       <c r="C214" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="215">
@@ -4209,7 +4209,7 @@
         <v>425</v>
       </c>
       <c r="C215" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="216">
@@ -4220,7 +4220,7 @@
         <v>427</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="217">
@@ -4231,7 +4231,7 @@
         <v>429</v>
       </c>
       <c r="C217" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="218">
@@ -4308,7 +4308,7 @@
         <v>443</v>
       </c>
       <c r="C224" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="225">
@@ -4319,7 +4319,7 @@
         <v>445</v>
       </c>
       <c r="C225" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="226">
@@ -4396,7 +4396,7 @@
         <v>458</v>
       </c>
       <c r="C232" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="233">
@@ -4440,7 +4440,7 @@
         <v>466</v>
       </c>
       <c r="C236" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="237">
@@ -4451,7 +4451,7 @@
         <v>468</v>
       </c>
       <c r="C237" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="238">
@@ -4462,7 +4462,7 @@
         <v>469</v>
       </c>
       <c r="C238" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="239">
@@ -4473,7 +4473,7 @@
         <v>471</v>
       </c>
       <c r="C239" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="240">
@@ -4484,7 +4484,7 @@
         <v>473</v>
       </c>
       <c r="C240" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="241">
@@ -4590,7 +4590,7 @@
         <v>491</v>
       </c>
       <c r="C250" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="251">

--- a/plots/map-data.xlsx
+++ b/plots/map-data.xlsx
@@ -2920,7 +2920,7 @@
         <v>199</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -2986,7 +2986,7 @@
         <v>211</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
@@ -4601,7 +4601,7 @@
         <v>493</v>
       </c>
       <c r="C251" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="252">
